--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014098</t>
+          <t xml:space="preserve">200014104</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311608660</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">

--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbækvej 20</t>
+          <t xml:space="preserve">Eriksvej 40A</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808161</t>
+          <t xml:space="preserve">5308263</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="J21">
-        <v>821</v>
+        <v>661</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 40A</t>
+          <t xml:space="preserve">Eriksvej 50B</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,16 +1626,16 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308263</t>
+          <t xml:space="preserve">719268, 5308429</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J22">
-        <v>661</v>
+        <v>266</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 50B</t>
+          <t xml:space="preserve">Frederiksborgvej 21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">719268, 5308429</t>
+          <t xml:space="preserve">5304824</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="J23">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 21</t>
+          <t xml:space="preserve">Gulddyssevej 70</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,16 +1776,16 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304824</t>
+          <t xml:space="preserve">8919779</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J24">
-        <v>254</v>
+        <v>472</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gulddyssevej 70</t>
+          <t xml:space="preserve">Haraldsborgvej 78</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8919779</t>
+          <t xml:space="preserve">5305533</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J25">
-        <v>472</v>
+        <v>912</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haraldsborgvej 78</t>
+          <t xml:space="preserve">Havnevej 47B</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5305533</t>
+          <t xml:space="preserve">719175, 5305606</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="J26">
-        <v>912</v>
+        <v>1440</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 47B</t>
+          <t xml:space="preserve">Herregårdsvej 46</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,16 +2001,16 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">719175, 5305606</t>
+          <t xml:space="preserve">2172704</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J27">
-        <v>1440</v>
+        <v>469</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 46</t>
+          <t xml:space="preserve">Herregårdsvej 48</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,16 +2076,16 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172704</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J28">
-        <v>469</v>
+        <v>1318</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 48</t>
+          <t xml:space="preserve">Herregårdsvej 61</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,16 +2151,16 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">9888274</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J29">
-        <v>1318</v>
+        <v>1776</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2231,11 +2231,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J30">
-        <v>1776</v>
+        <v>788</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 61</t>
+          <t xml:space="preserve">Himmelev Bygade 15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,16 +2301,16 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888274</t>
+          <t xml:space="preserve">9883833</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>788</v>
+        <v>378</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 15</t>
+          <t xml:space="preserve">Himmelev Bygade 22A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883833</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="J32">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 22A</t>
+          <t xml:space="preserve">Indfaldet 4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,16 +2451,16 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">5308164</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
       <c r="J33">
-        <v>405</v>
+        <v>5006</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indfaldet 4</t>
+          <t xml:space="preserve">Kildegården 1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,16 +2526,16 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308164</t>
+          <t xml:space="preserve">5309842</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J34">
-        <v>5006</v>
+        <v>4510</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 1</t>
+          <t xml:space="preserve">Kildegården 10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,16 +2601,16 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309842</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J35">
-        <v>4510</v>
+        <v>261</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 10</t>
+          <t xml:space="preserve">Kildegården 13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2681,11 +2681,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J36">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 13</t>
+          <t xml:space="preserve">Kildegården 2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2756,11 +2756,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J37">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 2</t>
+          <t xml:space="preserve">Kildegården 5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2831,11 +2831,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J38">
-        <v>307</v>
+        <v>1747</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 5</t>
+          <t xml:space="preserve">Kildegården 6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J39">
-        <v>1747</v>
+        <v>3208</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 6</t>
+          <t xml:space="preserve">Kildegården 7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,16 +2976,16 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">100197946</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J40">
-        <v>3208</v>
+        <v>392</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 7</t>
+          <t xml:space="preserve">Kildegården 8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,16 +3051,16 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">100197946</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J41">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 8</t>
+          <t xml:space="preserve">Kildegården 9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3131,11 +3131,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J42">
-        <v>291</v>
+        <v>883</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 9</t>
+          <t xml:space="preserve">Kongebakken 19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,16 +3201,16 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J43">
-        <v>883</v>
+        <v>3994</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19</t>
+          <t xml:space="preserve">Krathusvænge 8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,16 +3276,16 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">100513821</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J44">
-        <v>3994</v>
+        <v>566</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krathusvænge 8</t>
+          <t xml:space="preserve">Kurhusvænge 6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,16 +3351,16 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513821</t>
+          <t xml:space="preserve">100513816</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J45">
-        <v>566</v>
+        <v>1204</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kurhusvænge 6</t>
+          <t xml:space="preserve">Københavnsvej 106G</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,16 +3426,16 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513816</t>
+          <t xml:space="preserve">100101318</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J46">
-        <v>1204</v>
+        <v>330</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 106G</t>
+          <t xml:space="preserve">Køgevej 5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,16 +3501,16 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">100101318</t>
+          <t xml:space="preserve">8245209</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>330</v>
+        <v>764</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køgevej 5</t>
+          <t xml:space="preserve">Lindbjergvej 4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245209</t>
+          <t xml:space="preserve">2175641</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="J48">
-        <v>764</v>
+        <v>397</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindbjergvej 4</t>
+          <t xml:space="preserve">Lindevej 32</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175641</t>
+          <t xml:space="preserve">2217717</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="J49">
-        <v>397</v>
+        <v>586</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 32</t>
+          <t xml:space="preserve">Lindevej 34</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3731,11 +3731,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J50">
-        <v>586</v>
+        <v>2746</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3791,26 +3791,26 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 34</t>
+          <t xml:space="preserve">Læderstræde 6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217717</t>
+          <t xml:space="preserve">5303635</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J51">
-        <v>2746</v>
+        <v>632</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Læderstræde 6</t>
+          <t xml:space="preserve">Margrethehåbsvej 66</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303635</t>
+          <t xml:space="preserve">5313168</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="J52">
-        <v>632</v>
+        <v>819</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethehåbsvej 66</t>
+          <t xml:space="preserve">Margrethehåbsvej 68</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,16 +3951,16 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5313168</t>
+          <t xml:space="preserve">7969204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J53">
-        <v>819</v>
+        <v>1000</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethehåbsvej 68</t>
+          <t xml:space="preserve">Møllehusvej 13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,16 +4026,16 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969204</t>
+          <t xml:space="preserve">100069011</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J54">
-        <v>1000</v>
+        <v>5391</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,26 +4091,26 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 13</t>
+          <t xml:space="preserve">Møllevej 10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100069011</t>
+          <t xml:space="preserve">2175645</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55">
-        <v>5391</v>
+        <v>565</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4166,17 +4166,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 10</t>
+          <t xml:space="preserve">Nyvej 42</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175645</t>
+          <t xml:space="preserve">2213556</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="J56">
-        <v>565</v>
+        <v>335</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 42</t>
+          <t xml:space="preserve">Nyvej 52</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4256,11 +4256,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>335</v>
+        <v>469</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4316,26 +4316,26 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 52</t>
+          <t xml:space="preserve">Parcelgårdsvej 2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213556</t>
+          <t xml:space="preserve">100513811</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="J58">
-        <v>469</v>
+        <v>252</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelgårdsvej 2</t>
+          <t xml:space="preserve">Peblingevej 2B</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,16 +4401,16 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513811</t>
+          <t xml:space="preserve">8908094</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J59">
-        <v>252</v>
+        <v>692</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peblingevej 2B</t>
+          <t xml:space="preserve">Penselstrøget 62</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,16 +4476,16 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8908094</t>
+          <t xml:space="preserve">5308146</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J60">
-        <v>692</v>
+        <v>1740</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4541,26 +4541,26 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penselstrøget 62</t>
+          <t xml:space="preserve">Planetvej 30B</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308146</t>
+          <t xml:space="preserve">719295, 8907547</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="J61">
-        <v>1740</v>
+        <v>294</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,26 +4616,26 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planetvej 30B</t>
+          <t xml:space="preserve">Rabalderstræde 10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">719295, 8907547</t>
+          <t xml:space="preserve">8377662</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>294</v>
+        <v>553</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 10</t>
+          <t xml:space="preserve">Rabalderstræde 29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,16 +4701,16 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8377662</t>
+          <t xml:space="preserve">5308164</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">73</t>
         </is>
       </c>
       <c r="J63">
-        <v>553</v>
+        <v>462</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 29</t>
+          <t xml:space="preserve">Rabalderstræde 30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,16 +4776,16 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308164</t>
+          <t xml:space="preserve">719160, 5308146</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J64">
-        <v>462</v>
+        <v>1956</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4841,26 +4841,26 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 30</t>
+          <t xml:space="preserve">Ramsømaglevej 21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">719160, 5308146</t>
+          <t xml:space="preserve">2213458</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J65">
-        <v>1956</v>
+        <v>295</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4916,26 +4916,26 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 21</t>
+          <t xml:space="preserve">Rådmandshaven 4B</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213458</t>
+          <t xml:space="preserve">100096939</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J66">
-        <v>295</v>
+        <v>660</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådmandshaven 4B</t>
+          <t xml:space="preserve">Rønøs Alle 38</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,16 +5001,16 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100096939</t>
+          <t xml:space="preserve">5308584</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>660</v>
+        <v>497</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønøs Alle 38</t>
+          <t xml:space="preserve">Sandvejen 28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308584</t>
+          <t xml:space="preserve">719194, 2209303</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="J68">
-        <v>497</v>
+        <v>348</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvejen 28</t>
+          <t xml:space="preserve">Sankt Clara Vej 41</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,16 +5151,16 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">719194, 2209303</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J69">
-        <v>348</v>
+        <v>1980</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Clara Vej 41</t>
+          <t xml:space="preserve">Sankt Hans Gade 40</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,16 +5226,16 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">1352513</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>1980</v>
+        <v>525</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5291,26 +5291,26 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Hans Gade 40</t>
+          <t xml:space="preserve">Skovbrynet 4B</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352513</t>
+          <t xml:space="preserve">719337, 9604964</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J71">
-        <v>525</v>
+        <v>662</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4B</t>
+          <t xml:space="preserve">Skovbrynet 8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,16 +5376,16 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">719337, 9604964</t>
+          <t xml:space="preserve">9604965</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J72">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,26 +5441,26 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 8</t>
+          <t xml:space="preserve">Smedegade 21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9604965</t>
+          <t xml:space="preserve">1352516</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>622</v>
+        <v>590</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 21</t>
+          <t xml:space="preserve">Sognevej 4B</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352516</t>
+          <t xml:space="preserve">2171273</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="J74">
-        <v>590</v>
+        <v>300</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 4B</t>
+          <t xml:space="preserve">Spraglehøjvej 3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171273</t>
+          <t xml:space="preserve">100043785</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="J75">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,17 +5666,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spraglehøjvej 3</t>
+          <t xml:space="preserve">Store Valbyvej 150</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">100043785</t>
+          <t xml:space="preserve">2174609</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="J76">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 150</t>
+          <t xml:space="preserve">Store Valbyvej 248D</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174609</t>
+          <t xml:space="preserve">7343272</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="J77">
-        <v>313</v>
+        <v>1379</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 248D</t>
+          <t xml:space="preserve">Strandgade 12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7343272</t>
+          <t xml:space="preserve">719262, 9232188</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="J78">
-        <v>1379</v>
+        <v>440</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 12</t>
+          <t xml:space="preserve">Stændertorvet 19</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">719262, 9232188</t>
+          <t xml:space="preserve">5305072</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="J79">
-        <v>440</v>
+        <v>322</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 19</t>
+          <t xml:space="preserve">Stændertorvet 1B</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,16 +5976,16 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5305072</t>
+          <t xml:space="preserve">5304088</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
-        <v>322</v>
+        <v>852</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 1B</t>
+          <t xml:space="preserve">Stærkendevej 13</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,16 +6051,16 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304088</t>
+          <t xml:space="preserve">2209116</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J81">
-        <v>852</v>
+        <v>342</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stærkendevej 13</t>
+          <t xml:space="preserve">Søndre Alle 5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,16 +6126,16 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209116</t>
+          <t xml:space="preserve">100513824</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J82">
-        <v>342</v>
+        <v>280</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 5</t>
+          <t xml:space="preserve">Søndre Alle 7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,16 +6201,16 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513824</t>
+          <t xml:space="preserve">100513815</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="J83">
-        <v>280</v>
+        <v>475</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 7</t>
+          <t xml:space="preserve">Toftebakken 10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,16 +6276,16 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513815</t>
+          <t xml:space="preserve">100078592</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J84">
-        <v>475</v>
+        <v>288</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebakken 10</t>
+          <t xml:space="preserve">Toftebakken 11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6356,11 +6356,11 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J85">
-        <v>288</v>
+        <v>473</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebakken 11</t>
+          <t xml:space="preserve">Toftebakken 9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6431,11 +6431,11 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>473</v>
+        <v>323</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6491,17 +6491,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebakken 9</t>
+          <t xml:space="preserve">Tofthøjvej 11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078592</t>
+          <t xml:space="preserve">2217131</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="J87">
-        <v>323</v>
+        <v>866</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tofthøjvej 11</t>
+          <t xml:space="preserve">Vindeboder 12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217131</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="J88">
-        <v>866</v>
+        <v>1378</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 12</t>
+          <t xml:space="preserve">Vindeboder 20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="J89">
-        <v>1378</v>
+        <v>400</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6731,11 +6731,11 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J90">
-        <v>400</v>
+        <v>296</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6806,11 +6806,11 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J91">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 20</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,16 +6876,16 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">2170239</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J92">
-        <v>318</v>
+        <v>640</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 6</t>
+          <t xml:space="preserve">Ågerupvej 24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,16 +6951,16 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170239</t>
+          <t xml:space="preserve">2167528</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>640</v>
+        <v>444</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågerupvej 24</t>
+          <t xml:space="preserve">Darupvej 50</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167528</t>
+          <t xml:space="preserve">8995819</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,26 +7035,26 @@
         </is>
       </c>
       <c r="J94">
-        <v>444</v>
+        <v>1270</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014099</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BALSLEV</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darupvej 50</t>
+          <t xml:space="preserve">Sankt Hans Gade 4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995819</t>
+          <t xml:space="preserve">5304764</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>1270</v>
+        <v>709</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014099</t>
+          <t xml:space="preserve">200014102</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Hans Gade 4</t>
+          <t xml:space="preserve">Stærkendevej 15</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304764</t>
+          <t xml:space="preserve">2209116</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,11 +7185,11 @@
         </is>
       </c>
       <c r="J96">
-        <v>709</v>
+        <v>671</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014102</t>
+          <t xml:space="preserve">200014098</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stærkendevej 15</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 71</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209116</t>
+          <t xml:space="preserve">2170375</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7260,11 +7260,11 @@
         </is>
       </c>
       <c r="J97">
-        <v>671</v>
+        <v>290</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014104</t>
+          <t xml:space="preserve">200014100</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 71</t>
+          <t xml:space="preserve">Assendløsevejen 95</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170375</t>
+          <t xml:space="preserve">7516035</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,21 +7335,21 @@
         </is>
       </c>
       <c r="J98">
-        <v>290</v>
+        <v>950</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014100</t>
+          <t xml:space="preserve">200016725</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALSLEV</t>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-27</t>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,17 +7391,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assendløsevejen 95</t>
+          <t xml:space="preserve">Haraldsborgvej 80B</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7516035</t>
+          <t xml:space="preserve">2173125</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,11 +7410,11 @@
         </is>
       </c>
       <c r="J99">
-        <v>950</v>
+        <v>508</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016725</t>
+          <t xml:space="preserve">200016734</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7466,17 +7466,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haraldsborgvej 80B</t>
+          <t xml:space="preserve">Nyvej 38</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173125</t>
+          <t xml:space="preserve">2213439</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,11 +7485,11 @@
         </is>
       </c>
       <c r="J100">
-        <v>508</v>
+        <v>392</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016734</t>
+          <t xml:space="preserve">200016718</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 38</t>
+          <t xml:space="preserve">Nyvej 40</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7556,15 +7556,15 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>392</v>
+        <v>313</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016718</t>
+          <t xml:space="preserve">200016713</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,35 +7616,35 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 40</t>
+          <t xml:space="preserve">Præstemarksvænge 45</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213439</t>
+          <t xml:space="preserve">5306188</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016713</t>
+          <t xml:space="preserve">200016729</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstemarksvænge 45</t>
+          <t xml:space="preserve">Isafjordvej 1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306188</t>
+          <t xml:space="preserve">8727425</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,21 +7710,21 @@
         </is>
       </c>
       <c r="J103">
-        <v>351</v>
+        <v>796</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016729</t>
+          <t xml:space="preserve">200017082</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BALSLEV</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-07-07</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isafjordvej 1</t>
+          <t xml:space="preserve">Stormandshøjen 2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727425</t>
+          <t xml:space="preserve">9977521</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>796</v>
+        <v>940</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017082</t>
+          <t xml:space="preserve">200017379</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-07</t>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stormandshøjen 2</t>
+          <t xml:space="preserve">Baunehøjvej 50</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9977521</t>
+          <t xml:space="preserve">2175063</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>940</v>
+        <v>470</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017379</t>
+          <t xml:space="preserve">200017872</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 50</t>
+          <t xml:space="preserve">Himmelev Sognevej 115</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175063</t>
+          <t xml:space="preserve">8288838</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>470</v>
+        <v>586</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017872</t>
+          <t xml:space="preserve">200017864</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Sognevej 115</t>
+          <t xml:space="preserve">Ravnsholt 232</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8288838</t>
+          <t xml:space="preserve">2172779</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>586</v>
+        <v>703</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017864</t>
+          <t xml:space="preserve">200017863</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 232</t>
+          <t xml:space="preserve">Ravnsholt 236</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172779</t>
+          <t xml:space="preserve">2172775</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J108">
-        <v>703</v>
+        <v>598</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017863</t>
+          <t xml:space="preserve">200017862</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 236</t>
+          <t xml:space="preserve">Ravnsholt 238</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172775</t>
+          <t xml:space="preserve">2172727</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>598</v>
+        <v>747</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017862</t>
+          <t xml:space="preserve">200017861</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 238</t>
+          <t xml:space="preserve">Frederiksborgvej 9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172727</t>
+          <t xml:space="preserve">5304267</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>747</v>
+        <v>327</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017861</t>
+          <t xml:space="preserve">200017925</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-23</t>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 9</t>
+          <t xml:space="preserve">Lysalleen 31</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304267</t>
+          <t xml:space="preserve">2174435</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>327</v>
+        <v>814</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017925</t>
+          <t xml:space="preserve">200017906</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysalleen 31</t>
+          <t xml:space="preserve">Rådmandshaven 10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174435</t>
+          <t xml:space="preserve">8995859</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>814</v>
+        <v>1843</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017906</t>
+          <t xml:space="preserve">200017965</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-07-27</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådmandshaven 10</t>
+          <t xml:space="preserve">Eriksvej 23</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995859</t>
+          <t xml:space="preserve">8040594</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,21 +8460,21 @@
         </is>
       </c>
       <c r="J113">
-        <v>1843</v>
+        <v>750</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017965</t>
+          <t xml:space="preserve">200018664</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALSLEV</t>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-27</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 23</t>
+          <t xml:space="preserve">Galpestykket 555</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040594</t>
+          <t xml:space="preserve">2181467</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>750</v>
+        <v>615</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018664</t>
+          <t xml:space="preserve">200018663</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galpestykket 555</t>
+          <t xml:space="preserve">Hyrdehøj 60</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181467</t>
+          <t xml:space="preserve">9113192</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018663</t>
+          <t xml:space="preserve">200018667</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 60</t>
+          <t xml:space="preserve">Kastelsvej 2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113192</t>
+          <t xml:space="preserve">5304625</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>590</v>
+        <v>847</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018667</t>
+          <t xml:space="preserve">200018662</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastelsvej 2</t>
+          <t xml:space="preserve">Troldehøj 2</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304625</t>
+          <t xml:space="preserve">8995933</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>847</v>
+        <v>872</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018662</t>
+          <t xml:space="preserve">200018666</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troldehøj 2</t>
+          <t xml:space="preserve">Tunevej 10</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995933</t>
+          <t xml:space="preserve">8971417</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,11 +8835,11 @@
         </is>
       </c>
       <c r="J118">
-        <v>872</v>
+        <v>525</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018666</t>
+          <t xml:space="preserve">200018668</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tunevej 10</t>
+          <t xml:space="preserve">Vestergade 104</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971417</t>
+          <t xml:space="preserve">5312134</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>525</v>
+        <v>965</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018668</t>
+          <t xml:space="preserve">200018671</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 104</t>
+          <t xml:space="preserve">Vestergade 17A</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312134</t>
+          <t xml:space="preserve">10036944</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,11 +8985,11 @@
         </is>
       </c>
       <c r="J120">
-        <v>965</v>
+        <v>899</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018671</t>
+          <t xml:space="preserve">200020248</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-10</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 17A</t>
+          <t xml:space="preserve">Eriksvej 21</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">10036944</t>
+          <t xml:space="preserve">8225803</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="J121">
-        <v>899</v>
+        <v>414</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020248</t>
+          <t xml:space="preserve">200020461</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-10</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 21</t>
+          <t xml:space="preserve">Baunegårdsvej 70</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225803</t>
+          <t xml:space="preserve">2178666</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,21 +9135,21 @@
         </is>
       </c>
       <c r="J122">
-        <v>414</v>
+        <v>479</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020461</t>
+          <t xml:space="preserve">200020771</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 70</t>
+          <t xml:space="preserve">Bodsbjerggårdsvej 48</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178666</t>
+          <t xml:space="preserve">2216626</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>479</v>
+        <v>555</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020771</t>
+          <t xml:space="preserve">200020779</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bodsbjerggårdsvej 48</t>
+          <t xml:space="preserve">Bueager 5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216626</t>
+          <t xml:space="preserve">2211212</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>555</v>
+        <v>372</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020779</t>
+          <t xml:space="preserve">200020775</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 5</t>
+          <t xml:space="preserve">Bygaden 19</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211212</t>
+          <t xml:space="preserve">2176798</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>372</v>
+        <v>253</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020775</t>
+          <t xml:space="preserve">200020773</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 19</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 39</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176798</t>
+          <t xml:space="preserve">5304862</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>253</v>
+        <v>922</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020773</t>
+          <t xml:space="preserve">200020780</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 39</t>
+          <t xml:space="preserve">Lyngbakken 7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304862</t>
+          <t xml:space="preserve">2180449</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>922</v>
+        <v>403</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020780</t>
+          <t xml:space="preserve">200020831</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,30 +9566,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakken 7</t>
+          <t xml:space="preserve">Ramsømaglevej 21</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180449</t>
+          <t xml:space="preserve">2213458</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J128">
-        <v>403</v>
+        <v>311</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020831</t>
+          <t xml:space="preserve">200020830</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 21</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213458</t>
+          <t xml:space="preserve">9044555</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>311</v>
+        <v>1015</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020830</t>
+          <t xml:space="preserve">200020789</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Skovbrynet 6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9044555</t>
+          <t xml:space="preserve">9604963</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>1015</v>
+        <v>879</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020789</t>
+          <t xml:space="preserve">200020787</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 6</t>
+          <t xml:space="preserve">Wiemosen 1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9604963</t>
+          <t xml:space="preserve">5310765</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>879</v>
+        <v>733</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020787</t>
+          <t xml:space="preserve">200020827</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wiemosen 1</t>
+          <t xml:space="preserve">Ågeruphøj 2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310765</t>
+          <t xml:space="preserve">2167811</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>733</v>
+        <v>372</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020827</t>
+          <t xml:space="preserve">200020826</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågeruphøj 2</t>
+          <t xml:space="preserve">Ørstedvej 61A</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167811</t>
+          <t xml:space="preserve">8948799</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>372</v>
+        <v>581</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020826</t>
+          <t xml:space="preserve">200020772</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 61A</t>
+          <t xml:space="preserve">Ørstedvej 61B</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948799</t>
+          <t xml:space="preserve">7940083</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020772</t>
+          <t xml:space="preserve">200020777</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 61B</t>
+          <t xml:space="preserve">Ravnsholt 234</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7940083</t>
+          <t xml:space="preserve">2172733</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,21 +10110,21 @@
         </is>
       </c>
       <c r="J135">
-        <v>601</v>
+        <v>407</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020777</t>
+          <t xml:space="preserve">200023413</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-04</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 234</t>
+          <t xml:space="preserve">Algade 31</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172733</t>
+          <t xml:space="preserve">2174559</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>407</v>
+        <v>611</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023413</t>
+          <t xml:space="preserve">200023817</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-04</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 31</t>
+          <t xml:space="preserve">Møllevej 6</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174559</t>
+          <t xml:space="preserve">7054261</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J137">
-        <v>611</v>
+        <v>796</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023817</t>
+          <t xml:space="preserve">200023841</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 6</t>
+          <t xml:space="preserve">Rypevej 2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7054261</t>
+          <t xml:space="preserve">5306607</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,11 +10335,11 @@
         </is>
       </c>
       <c r="J138">
-        <v>796</v>
+        <v>423</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023841</t>
+          <t xml:space="preserve">200023835</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rypevej 2</t>
+          <t xml:space="preserve">Snebærvej 16</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306607</t>
+          <t xml:space="preserve">2209470</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J139">
-        <v>423</v>
+        <v>795</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023835</t>
+          <t xml:space="preserve">200023864</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snebærvej 16</t>
+          <t xml:space="preserve">Æblehaven 78</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209470</t>
+          <t xml:space="preserve">719221</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J140">
-        <v>795</v>
+        <v>482</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023864</t>
+          <t xml:space="preserve">200023819</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10541,30 +10541,30 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblehaven 78</t>
+          <t xml:space="preserve">Agerskellet 13</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">719221</t>
+          <t xml:space="preserve">7568845</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>482</v>
+        <v>354</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023819</t>
+          <t xml:space="preserve">200023910</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-11-13</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agerskellet 13</t>
+          <t xml:space="preserve">Frederiksborgvej 561</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568845</t>
+          <t xml:space="preserve">2178448</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023910</t>
+          <t xml:space="preserve">200023938</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,40 +10691,40 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 561</t>
+          <t xml:space="preserve">Grantoften 3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178448</t>
+          <t xml:space="preserve">2217322</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023938</t>
+          <t xml:space="preserve">200024857</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 3</t>
+          <t xml:space="preserve">Grantoften 5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J144">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 5</t>
+          <t xml:space="preserve">Hyrdehøj 62</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217322</t>
+          <t xml:space="preserve">9113193</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>392</v>
+        <v>722</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024857</t>
+          <t xml:space="preserve">200024858</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 62</t>
+          <t xml:space="preserve">Kornvej 1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113193</t>
+          <t xml:space="preserve">8550293</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>722</v>
+        <v>812</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024858</t>
+          <t xml:space="preserve">200024855</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kornvej 1</t>
+          <t xml:space="preserve">Dommervænget 30</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550293</t>
+          <t xml:space="preserve">5306255</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>812</v>
+        <v>1225</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024855</t>
+          <t xml:space="preserve">200024872</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2019-12-02</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dommervænget 30</t>
+          <t xml:space="preserve">Bygaden 28</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306255</t>
+          <t xml:space="preserve">2178710</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>1225</v>
+        <v>263</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024872</t>
+          <t xml:space="preserve">200024953</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-02</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28</t>
+          <t xml:space="preserve">Gammel Darupvej 3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178710</t>
+          <t xml:space="preserve">5307880</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>263</v>
+        <v>1383</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024953</t>
+          <t xml:space="preserve">200024956</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Darupvej 3</t>
+          <t xml:space="preserve">Lysalleen 33</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307880</t>
+          <t xml:space="preserve">8717244</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>1383</v>
+        <v>1298</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024956</t>
+          <t xml:space="preserve">200024948</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysalleen 33</t>
+          <t xml:space="preserve">Eriksvej 40C</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,20 +11301,20 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8717244</t>
+          <t xml:space="preserve">5308364</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J151">
-        <v>1298</v>
+        <v>852</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024948</t>
+          <t xml:space="preserve">200024993</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 40C</t>
+          <t xml:space="preserve">Københavnsvej 106C</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308364</t>
+          <t xml:space="preserve">7896055</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>852</v>
+        <v>680</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024993</t>
+          <t xml:space="preserve">200024994</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 106C</t>
+          <t xml:space="preserve">Kamstrupsti 2</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896055</t>
+          <t xml:space="preserve">5308151</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>680</v>
+        <v>400</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024994</t>
+          <t xml:space="preserve">200027969</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupsti 2</t>
+          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,30 +11526,30 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308151</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J154">
-        <v>400</v>
+        <v>995</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027969</t>
+          <t xml:space="preserve">200030999</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">BALSLEV</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2020-05-03</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
+          <t xml:space="preserve">Astersvej 9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,30 +11601,30 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">5308975</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>995</v>
+        <v>4292</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030999</t>
+          <t xml:space="preserve">200049549</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALSLEV</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-03</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 9</t>
+          <t xml:space="preserve">Stændertorvet 1D</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308975</t>
+          <t xml:space="preserve">5304086</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>4292</v>
+        <v>1906</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049549</t>
+          <t xml:space="preserve">200050785</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2021-06-29</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 1D</t>
+          <t xml:space="preserve">Mosestykket 21</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304086</t>
+          <t xml:space="preserve">2208892</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J157">
-        <v>1906</v>
+        <v>770</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050785</t>
+          <t xml:space="preserve">200051688</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-29</t>
+          <t xml:space="preserve">2021-08-03</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosestykket 21</t>
+          <t xml:space="preserve">Københavnsvej 266</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,30 +11826,30 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208892</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>770</v>
+        <v>573</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051688</t>
+          <t xml:space="preserve">200057196</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Forum r.i.</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-03</t>
+          <t xml:space="preserve">2022-02-06</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266</t>
+          <t xml:space="preserve">Møllehusvej 13</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">8135053</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,21 +11910,21 @@
         </is>
       </c>
       <c r="J159">
-        <v>573</v>
+        <v>9546</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057196</t>
+          <t xml:space="preserve">200057529</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forum r.i.</t>
+          <t xml:space="preserve">TopDahl ApS</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-06</t>
+          <t xml:space="preserve">2022-02-20</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 13</t>
+          <t xml:space="preserve">Herregårdsvej 42</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8135053</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>9546</v>
+        <v>1898</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057529</t>
+          <t xml:space="preserve">200057621</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-20</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 42</t>
+          <t xml:space="preserve">Tranevej 7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">7938930</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,21 +12060,21 @@
         </is>
       </c>
       <c r="J161">
-        <v>1898</v>
+        <v>638</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057621</t>
+          <t xml:space="preserve">200060567</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">TopDahl ApS</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 7</t>
+          <t xml:space="preserve">Baunegårdsvej 80</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,30 +12126,30 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938930</t>
+          <t xml:space="preserve">2179645</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060567</t>
+          <t xml:space="preserve">311052501</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-29</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,40 +12191,40 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 80</t>
+          <t xml:space="preserve">Højbakken 2</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179645</t>
+          <t xml:space="preserve">10229610</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J163">
-        <v>677</v>
+        <v>620</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311052501</t>
+          <t xml:space="preserve">311060924</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12281,11 +12281,11 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J164">
-        <v>620</v>
+        <v>1226</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbakken 2</t>
+          <t xml:space="preserve">Baunehøjvej 5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,30 +12351,30 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">10229610</t>
+          <t xml:space="preserve">2174626</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>1226</v>
+        <v>287</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311060924</t>
+          <t xml:space="preserve">311082107</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-23</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 5</t>
+          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174626</t>
+          <t xml:space="preserve">5309424</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>287</v>
+        <v>2196</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082107</t>
+          <t xml:space="preserve">311082106</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
+          <t xml:space="preserve">Himmelev Bygade 22C</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309424</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J167">
-        <v>2196</v>
+        <v>426</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082106</t>
+          <t xml:space="preserve">311082104</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 22C</t>
+          <t xml:space="preserve">Bistruphøj 2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">5312115</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>426</v>
+        <v>1048</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082104</t>
+          <t xml:space="preserve">311083539</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistruphøj 2</t>
+          <t xml:space="preserve">Bistrupvænge 16</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,25 +12651,25 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312115</t>
+          <t xml:space="preserve">5312015</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="J169">
-        <v>1048</v>
+        <v>927</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083539</t>
+          <t xml:space="preserve">311083529</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvænge 16</t>
+          <t xml:space="preserve">Lindegårdsparken 1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">139</t>
         </is>
       </c>
       <c r="J170">
-        <v>927</v>
+        <v>20718</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsparken 1</t>
+          <t xml:space="preserve">Nygade 13</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,30 +12801,30 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312015</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>20718</v>
+        <v>568</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083529</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-14</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 13</t>
+          <t xml:space="preserve">Nygade 14</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 14</t>
+          <t xml:space="preserve">Nygade 18</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J173">
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 18</t>
+          <t xml:space="preserve">Rosenhaven 13</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J174">
-        <v>568</v>
+        <v>268</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311098182</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 13</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2174669</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>268</v>
+        <v>401</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098182</t>
+          <t xml:space="preserve">311101306</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-03-17</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Sankt Ols Stræde 5</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174669</t>
+          <t xml:space="preserve">5303417</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101306</t>
+          <t xml:space="preserve">311109494</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-17</t>
+          <t xml:space="preserve">2025-04-28</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 5</t>
+          <t xml:space="preserve">Strandgade 2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303417</t>
+          <t xml:space="preserve">5312664, 100884612</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J177">
-        <v>482</v>
+        <v>345</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109494</t>
+          <t xml:space="preserve">311110647</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-28</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 2</t>
+          <t xml:space="preserve">Lammegade 26</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312664, 100884612</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J178">
-        <v>345</v>
+        <v>667</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110647</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 26</t>
+          <t xml:space="preserve">Lammegade 28</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J179">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 28</t>
+          <t xml:space="preserve">Lammegade 30</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J180">
-        <v>667</v>
+        <v>496</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 30</t>
+          <t xml:space="preserve">Lammegade 36</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13556,11 +13556,11 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J181">
-        <v>496</v>
+        <v>624</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 36</t>
+          <t xml:space="preserve">Vestergade 6A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">5312565</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>624</v>
+        <v>3282</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311115034</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 6A</t>
+          <t xml:space="preserve">Lyngbakken 1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312565</t>
+          <t xml:space="preserve">7175316</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>3282</v>
+        <v>362</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115034</t>
+          <t xml:space="preserve">311118205</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakken 1</t>
+          <t xml:space="preserve">Navervej 16</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7175316</t>
+          <t xml:space="preserve">2209531</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>362</v>
+        <v>1432</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118205</t>
+          <t xml:space="preserve">311124782</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-10</t>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13856,11 +13856,11 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J185">
-        <v>1432</v>
+        <v>979</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navervej 16</t>
+          <t xml:space="preserve">Rabalderstræde 16</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209531</t>
+          <t xml:space="preserve">719145, 100067704</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,21 +13935,21 @@
         </is>
       </c>
       <c r="J186">
-        <v>979</v>
+        <v>3529</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124782</t>
+          <t xml:space="preserve">311137096</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-13</t>
+          <t xml:space="preserve">2025-09-28</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 16</t>
+          <t xml:space="preserve">Jernbanegade 21A</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,30 +14001,30 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">719145, 100067704</t>
+          <t xml:space="preserve">8995769</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>3529</v>
+        <v>1236</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311137096</t>
+          <t xml:space="preserve">311162791</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-28</t>
+          <t xml:space="preserve">2026-03-07</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 21A</t>
+          <t xml:space="preserve">Vestre Hedevej 32</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,40 +14076,40 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995769</t>
+          <t xml:space="preserve">719290, 100013803</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J188">
-        <v>1236</v>
+        <v>276</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311162791</t>
+          <t xml:space="preserve">311241595</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-07</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Hedevej 32</t>
+          <t xml:space="preserve">Basgangen 20</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,20 +14151,20 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">719290, 100013803</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="J189">
-        <v>276</v>
+        <v>2980</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241595</t>
+          <t xml:space="preserve">311351867</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2028-12-17</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basgangen 20</t>
+          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,30 +14226,30 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">100122346</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>2980</v>
+        <v>9549</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351867</t>
+          <t xml:space="preserve">311522399</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-17</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,40 +14291,40 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
+          <t xml:space="preserve">Søndergade 11</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">100122346</t>
+          <t xml:space="preserve">7855029</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J191">
-        <v>9549</v>
+        <v>1530</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522399</t>
+          <t xml:space="preserve">311552201</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,40 +14366,40 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 11</t>
+          <t xml:space="preserve">Sandhøjsvej 4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7855029</t>
+          <t xml:space="preserve">1304635</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>1530</v>
+        <v>599</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552201</t>
+          <t xml:space="preserve">311569226</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandhøjsvej 4</t>
+          <t xml:space="preserve">Ramsømaglevej 17B</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304635</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>599</v>
+        <v>1459</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569226</t>
+          <t xml:space="preserve">311570325</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17B</t>
+          <t xml:space="preserve">Ramsømaglevej 17D</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14531,15 +14531,15 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J194">
-        <v>1459</v>
+        <v>355</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570325</t>
+          <t xml:space="preserve">311570327</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14591,40 +14591,40 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17D</t>
+          <t xml:space="preserve">Ejboparken 6</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J195">
-        <v>355</v>
+        <v>435</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570327</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6</t>
+          <t xml:space="preserve">Ejboparken 6B</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14681,11 +14681,11 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J196">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J197">
-        <v>517</v>
+        <v>258</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6B</t>
+          <t xml:space="preserve">Ejboparken 8A</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14831,11 +14831,11 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J198">
-        <v>258</v>
+        <v>477</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 8A</t>
+          <t xml:space="preserve">Hørhusene 61</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,20 +14901,20 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">5312139</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>477</v>
+        <v>826</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311595512</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørhusene 61</t>
+          <t xml:space="preserve">Københavnsvej 266C</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,30 +14976,30 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312139</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J200">
-        <v>826</v>
+        <v>322</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595512</t>
+          <t xml:space="preserve">311587049</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-22</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,40 +15041,40 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266C</t>
+          <t xml:space="preserve">Bueager 8</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">2211135</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J201">
-        <v>322</v>
+        <v>469</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587049</t>
+          <t xml:space="preserve">311608657</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">2032-06-17</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 8</t>
+          <t xml:space="preserve">Bueager 2</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15131,15 +15131,15 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J202">
-        <v>469</v>
+        <v>4564</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608660</t>
+          <t xml:space="preserve">311610029</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-17</t>
+          <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15206,11 +15206,11 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J203">
-        <v>4564</v>
+        <v>2127</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15281,11 +15281,11 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J204">
-        <v>2127</v>
+        <v>847</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 2</t>
+          <t xml:space="preserve">Bueager 6</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15356,15 +15356,15 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J205">
-        <v>847</v>
+        <v>1898</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610029</t>
+          <t xml:space="preserve">311610041</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15416,40 +15416,40 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 6</t>
+          <t xml:space="preserve">Køgevej 106</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211135</t>
+          <t xml:space="preserve">5308417</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J206">
-        <v>1898</v>
+        <v>1620</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610041</t>
+          <t xml:space="preserve">311626283</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-23</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,40 +15491,40 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køgevej 106</t>
+          <t xml:space="preserve">Snoldelev Bygade 21B</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308417</t>
+          <t xml:space="preserve">2202050</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>1620</v>
+        <v>438</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626283</t>
+          <t xml:space="preserve">311633105</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snoldelev Bygade 21B</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202050</t>
+          <t xml:space="preserve">2170541</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>438</v>
+        <v>1257</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633105</t>
+          <t xml:space="preserve">311633102</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170541</t>
+          <t xml:space="preserve">8016122</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,21 +15660,21 @@
         </is>
       </c>
       <c r="J209">
-        <v>1257</v>
+        <v>2104</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633102</t>
+          <t xml:space="preserve">311645050</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-04</t>
+          <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15731,11 +15731,11 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J210">
-        <v>2104</v>
+        <v>434</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
+          <t xml:space="preserve">Gundsølillevej 2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,30 +15801,30 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">8016122</t>
+          <t xml:space="preserve">2167605</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J211">
-        <v>434</v>
+        <v>979</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645050</t>
+          <t xml:space="preserve">311643576</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-08</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 2</t>
+          <t xml:space="preserve">Gundsølillevej 6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15881,15 +15881,15 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J212">
-        <v>979</v>
+        <v>4101</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643576</t>
+          <t xml:space="preserve">311643577</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 6</t>
+          <t xml:space="preserve">Sognevej 50</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,20 +15951,20 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167605</t>
+          <t xml:space="preserve">2172270</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>4101</v>
+        <v>3519</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643577</t>
+          <t xml:space="preserve">311644570</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 50</t>
+          <t xml:space="preserve">Planetvej 30</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172270</t>
+          <t xml:space="preserve">8907547</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,21 +16035,21 @@
         </is>
       </c>
       <c r="J214">
-        <v>3519</v>
+        <v>897</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644570</t>
+          <t xml:space="preserve">311644810</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">BOTJEK A/S</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-23</t>
+          <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16106,11 +16106,11 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J215">
-        <v>897</v>
+        <v>398</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J216">
-        <v>398</v>
+        <v>1311</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J217">
-        <v>1311</v>
+        <v>924</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J218">
-        <v>924</v>
+        <v>487</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16406,11 +16406,11 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J219">
-        <v>487</v>
+        <v>256</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J220">
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J221">
-        <v>256</v>
+        <v>897</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J222">
-        <v>897</v>
+        <v>983</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J223">
-        <v>983</v>
+        <v>552</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J224">
-        <v>552</v>
+        <v>897</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J225">
@@ -16931,11 +16931,11 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J226">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -17006,11 +17006,11 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J227">
-        <v>898</v>
+        <v>280</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -17081,11 +17081,11 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J228">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -17156,11 +17156,11 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J229">
-        <v>900</v>
+        <v>789</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -17216,40 +17216,40 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planetvej 30</t>
+          <t xml:space="preserve">H H Kochs Vej 4</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">8907547</t>
+          <t xml:space="preserve">2173007</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J230">
-        <v>789</v>
+        <v>7796</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644810</t>
+          <t xml:space="preserve">311645058</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTJEK A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-24</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">H H Kochs Vej 4</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173007</t>
+          <t xml:space="preserve">2180519</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17310,16 +17310,16 @@
         </is>
       </c>
       <c r="J231">
-        <v>7796</v>
+        <v>1448</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645058</t>
+          <t xml:space="preserve">311644999</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -17381,11 +17381,11 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J232">
-        <v>1448</v>
+        <v>413</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Lindelunden 1</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180519</t>
+          <t xml:space="preserve">5306821</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17460,21 +17460,21 @@
         </is>
       </c>
       <c r="J233">
-        <v>413</v>
+        <v>5829</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644999</t>
+          <t xml:space="preserve">311645727</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindelunden 1</t>
+          <t xml:space="preserve">Trekroner Centervej 41</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17531,11 +17531,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J234">
-        <v>5829</v>
+        <v>12072</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17591,17 +17591,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Centervej 41</t>
+          <t xml:space="preserve">Ramsømaglevej 19</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306821</t>
+          <t xml:space="preserve">2213437</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,11 +17610,11 @@
         </is>
       </c>
       <c r="J235">
-        <v>12072</v>
+        <v>2744</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645727</t>
+          <t xml:space="preserve">311646168</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17681,15 +17681,15 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>2744</v>
+        <v>1287</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646168</t>
+          <t xml:space="preserve">311646167</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 19</t>
+          <t xml:space="preserve">Gammel Vindingevej 10</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213437</t>
+          <t xml:space="preserve">2209330</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>1287</v>
+        <v>5956</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646167</t>
+          <t xml:space="preserve">311646682</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17831,15 +17831,15 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J238">
-        <v>5956</v>
+        <v>447</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646682</t>
+          <t xml:space="preserve">311646683</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Vindingevej 10</t>
+          <t xml:space="preserve">Margrethekær 2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,20 +17901,20 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209330</t>
+          <t xml:space="preserve">9700889</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J239">
-        <v>447</v>
+        <v>2442</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646683</t>
+          <t xml:space="preserve">311647649</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 2</t>
+          <t xml:space="preserve">Margrethekær 10</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17981,15 +17981,15 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J240">
-        <v>2442</v>
+        <v>1500</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647649</t>
+          <t xml:space="preserve">311647742</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 10</t>
+          <t xml:space="preserve">Margrethekær 12</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J241">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 12</t>
+          <t xml:space="preserve">Margrethekær 4</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J242">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 4</t>
+          <t xml:space="preserve">Margrethekær 6</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18206,11 +18206,11 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J243">
-        <v>1514</v>
+        <v>1500</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 6</t>
+          <t xml:space="preserve">Margrethekær 8</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18281,11 +18281,11 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J244">
-        <v>1500</v>
+        <v>1577</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 8</t>
+          <t xml:space="preserve">Hyrdehøj 3</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,30 +18351,30 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700889</t>
+          <t xml:space="preserve">7713101</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>1577</v>
+        <v>11744</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647742</t>
+          <t xml:space="preserve">311649946</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18431,15 +18431,15 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J246">
-        <v>11744</v>
+        <v>1185</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649946</t>
+          <t xml:space="preserve">311649970</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2032-12-18</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 3</t>
+          <t xml:space="preserve">Møllehusvej 118</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,30 +18501,30 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">7713101</t>
+          <t xml:space="preserve">258624, 258625</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J247">
-        <v>1185</v>
+        <v>4232</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649970</t>
+          <t xml:space="preserve">311650857</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-18</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,17 +18566,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 118</t>
+          <t xml:space="preserve">Kirkebjergvej 2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">258624, 258625</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,11 +18585,11 @@
         </is>
       </c>
       <c r="J248">
-        <v>4232</v>
+        <v>1786</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650857</t>
+          <t xml:space="preserve">311652564</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 2</t>
+          <t xml:space="preserve">Kirkebjergvej 4</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18656,15 +18656,15 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J249">
-        <v>1786</v>
+        <v>1585</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652564</t>
+          <t xml:space="preserve">311652563</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 4</t>
+          <t xml:space="preserve">Kirkebjergvej 6</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18731,15 +18731,15 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J250">
-        <v>1585</v>
+        <v>2239</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652563</t>
+          <t xml:space="preserve">311652567</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 6</t>
+          <t xml:space="preserve">Kirkebjergvej 8</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18806,15 +18806,15 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J251">
-        <v>2239</v>
+        <v>610</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652567</t>
+          <t xml:space="preserve">311652565</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18866,40 +18866,40 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 8</t>
+          <t xml:space="preserve">Ørstedvej 63B</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J252">
-        <v>610</v>
+        <v>8368</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652565</t>
+          <t xml:space="preserve">311652748</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-01-06</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,40 +18941,40 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63B</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J253">
-        <v>8368</v>
+        <v>1815</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652748</t>
+          <t xml:space="preserve">311652906</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-06</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19031,11 +19031,11 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J254">
-        <v>1815</v>
+        <v>2850</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -19106,11 +19106,11 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J255">
-        <v>2850</v>
+        <v>1908</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -19166,40 +19166,40 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">5304953</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J256">
-        <v>1908</v>
+        <v>6173</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652906</t>
+          <t xml:space="preserve">311656342</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
+          <t xml:space="preserve">Københavnsvej 34</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304953</t>
+          <t xml:space="preserve">5311321</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -19260,21 +19260,21 @@
         </is>
       </c>
       <c r="J257">
-        <v>6173</v>
+        <v>9899</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656342</t>
+          <t xml:space="preserve">311655694</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 34</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,25 +19326,25 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311321</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J258">
-        <v>9899</v>
+        <v>9084</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655694</t>
+          <t xml:space="preserve">311655558</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Bymarken 37</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,20 +19401,20 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5306248</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J259">
-        <v>9084</v>
+        <v>8569</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655558</t>
+          <t xml:space="preserve">311656548</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymarken 37</t>
+          <t xml:space="preserve">Gormsvej 9B</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,20 +19476,20 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306248</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J260">
-        <v>8569</v>
+        <v>440</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656548</t>
+          <t xml:space="preserve">311656782</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 9B</t>
+          <t xml:space="preserve">Rådhusbuen 3</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19556,15 +19556,15 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J261">
-        <v>440</v>
+        <v>5709</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656782</t>
+          <t xml:space="preserve">311657131</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-30</t>
+          <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 3</t>
+          <t xml:space="preserve">Munkebro 2</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19626,20 +19626,20 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5303415</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J262">
-        <v>5709</v>
+        <v>608</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657131</t>
+          <t xml:space="preserve">311657447</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-31</t>
+          <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkebro 2</t>
+          <t xml:space="preserve">Sankt Ols Stræde 3</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19706,15 +19706,15 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J263">
-        <v>608</v>
+        <v>858</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657447</t>
+          <t xml:space="preserve">311657449</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19781,15 +19781,15 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J264">
-        <v>858</v>
+        <v>433</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657449</t>
+          <t xml:space="preserve">311657448</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 3</t>
+          <t xml:space="preserve">Absalonsgade 1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303415</t>
+          <t xml:space="preserve">8995768</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,21 +19860,21 @@
         </is>
       </c>
       <c r="J265">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657448</t>
+          <t xml:space="preserve">311659172</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-01</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 1</t>
+          <t xml:space="preserve">Absalonsgade 2</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19931,11 +19931,11 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J266">
-        <v>378</v>
+        <v>6187</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 2</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995768</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,21 +20010,21 @@
         </is>
       </c>
       <c r="J267">
-        <v>6187</v>
+        <v>9651</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659172</t>
+          <t xml:space="preserve">311666198</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-14</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,17 +20066,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Baunegårdsvej 85</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -20085,21 +20085,21 @@
         </is>
       </c>
       <c r="J268">
-        <v>9651</v>
+        <v>3340</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666198</t>
+          <t xml:space="preserve">311664732</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-14</t>
+          <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20156,11 +20156,11 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J269">
-        <v>3340</v>
+        <v>916</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -20231,11 +20231,11 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J270">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -20306,11 +20306,11 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J271">
-        <v>900</v>
+        <v>711</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -20381,11 +20381,11 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J272">
-        <v>711</v>
+        <v>1816</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -20441,30 +20441,30 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 85</t>
+          <t xml:space="preserve">Lynghøjen 107A</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J273">
-        <v>1816</v>
+        <v>817</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664732</t>
+          <t xml:space="preserve">311665647</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-07</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107A</t>
+          <t xml:space="preserve">Lynghøjen 107B</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20531,15 +20531,15 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J274">
-        <v>817</v>
+        <v>1552</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665647</t>
+          <t xml:space="preserve">311665669</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107B</t>
+          <t xml:space="preserve">Lynghøjen 107C</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20606,11 +20606,11 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J275">
-        <v>1552</v>
+        <v>433</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107C</t>
+          <t xml:space="preserve">Lynghøjen 107</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20681,15 +20681,15 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J276">
-        <v>433</v>
+        <v>12308</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665669</t>
+          <t xml:space="preserve">311666274</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-03-14</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107</t>
+          <t xml:space="preserve">Industrileddet 4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">2180546</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -20760,21 +20760,21 @@
         </is>
       </c>
       <c r="J277">
-        <v>12308</v>
+        <v>2200</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666274</t>
+          <t xml:space="preserve">311666541</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-14</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrileddet 4</t>
+          <t xml:space="preserve">Ollerupvej 5</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180546</t>
+          <t xml:space="preserve">2173759</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -20835,21 +20835,21 @@
         </is>
       </c>
       <c r="J278">
-        <v>2200</v>
+        <v>12044</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666541</t>
+          <t xml:space="preserve">311667669</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-03-20</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20906,11 +20906,11 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J279">
-        <v>12044</v>
+        <v>494</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 5</t>
+          <t xml:space="preserve">Ollerupvej 7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20981,15 +20981,15 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J280">
-        <v>494</v>
+        <v>826</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667669</t>
+          <t xml:space="preserve">311667621</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 7</t>
+          <t xml:space="preserve">Helligkorsvej 42A</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -21051,20 +21051,20 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173759</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J281">
-        <v>826</v>
+        <v>3137</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667621</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-20</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21131,11 +21131,11 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J282">
-        <v>3137</v>
+        <v>6340</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -21206,11 +21206,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J283">
-        <v>6340</v>
+        <v>2165</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42A</t>
+          <t xml:space="preserve">Helligkorsvej 42C</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -21281,11 +21281,11 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J284">
-        <v>2165</v>
+        <v>778</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42C</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -21351,20 +21351,20 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J285">
-        <v>778</v>
+        <v>2177</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21431,11 +21431,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J286">
-        <v>2177</v>
+        <v>3318</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -21506,11 +21506,11 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J287">
-        <v>3318</v>
+        <v>766</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Østre Vindingevej 221C</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -21581,15 +21581,15 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J288">
-        <v>766</v>
+        <v>2100</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670926</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221C</t>
+          <t xml:space="preserve">Bistrup Bakke 5</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21651,30 +21651,30 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">100513814</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">109</t>
         </is>
       </c>
       <c r="J289">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670926</t>
+          <t xml:space="preserve">311673245</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 5</t>
+          <t xml:space="preserve">Bistrup Bakke 3</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -21731,15 +21731,15 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">109</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J290">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673245</t>
+          <t xml:space="preserve">311675948</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21749,7 +21749,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 3</t>
+          <t xml:space="preserve">Bistrup Bakke 7</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21806,15 +21806,15 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J291">
-        <v>997</v>
+        <v>1077</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675948</t>
+          <t xml:space="preserve">311675950</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 7</t>
+          <t xml:space="preserve">Astersvej 15</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -21876,30 +21876,30 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513814</t>
+          <t xml:space="preserve">8995869</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J292">
-        <v>1077</v>
+        <v>10347</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675950</t>
+          <t xml:space="preserve">311676003</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-24</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21956,11 +21956,11 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J293">
-        <v>10347</v>
+        <v>6038</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15</t>
+          <t xml:space="preserve">Astersvej 15C</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22031,15 +22031,15 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J294">
-        <v>6038</v>
+        <v>643</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676003</t>
+          <t xml:space="preserve">311676217</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -22091,30 +22091,30 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15C</t>
+          <t xml:space="preserve">Ørstedvej 63A</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995869</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J295">
-        <v>643</v>
+        <v>585</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676217</t>
+          <t xml:space="preserve">311679099</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,30 +22166,30 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63A</t>
+          <t xml:space="preserve">Kongebakken 19</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J296">
-        <v>585</v>
+        <v>6671</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679099</t>
+          <t xml:space="preserve">311683094</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-25</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19</t>
+          <t xml:space="preserve">Kongebakken 19A</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">9306001</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -22260,11 +22260,11 @@
         </is>
       </c>
       <c r="J297">
-        <v>6671</v>
+        <v>630</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683094</t>
+          <t xml:space="preserve">311683580</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-25</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19A</t>
+          <t xml:space="preserve">Trekroner Alle 1</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306001</t>
+          <t xml:space="preserve">2174448</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -22335,11 +22335,11 @@
         </is>
       </c>
       <c r="J298">
-        <v>630</v>
+        <v>1216</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683580</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-26</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -22406,11 +22406,11 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J299">
-        <v>1216</v>
+        <v>1537</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -22481,11 +22481,11 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J300">
-        <v>1537</v>
+        <v>962</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -22556,11 +22556,11 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J301">
-        <v>962</v>
+        <v>3144</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -22631,11 +22631,11 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J302">
-        <v>3144</v>
+        <v>929</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -22706,11 +22706,11 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J303">
-        <v>929</v>
+        <v>553</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -22781,11 +22781,11 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J304">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
@@ -22856,15 +22856,15 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J305">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725441</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22931,15 +22931,15 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J306">
-        <v>599</v>
+        <v>715</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725441</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1</t>
+          <t xml:space="preserve">Trekroner Alle 1C</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23006,15 +23006,15 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J307">
-        <v>715</v>
+        <v>2011</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725438</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1C</t>
+          <t xml:space="preserve">Piledyssen 50</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23076,30 +23076,30 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174448</t>
+          <t xml:space="preserve">2172114</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J308">
-        <v>2011</v>
+        <v>595</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725438</t>
+          <t xml:space="preserve">311743780</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledyssen 50</t>
+          <t xml:space="preserve">Vindeboder 7</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -23151,30 +23151,30 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172114</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J309">
-        <v>595</v>
+        <v>686</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743780</t>
+          <t xml:space="preserve">311787742</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-07</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23231,11 +23231,11 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J310">
-        <v>686</v>
+        <v>452</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -23306,15 +23306,15 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J311">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787742</t>
+          <t xml:space="preserve">311787741</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -23381,15 +23381,15 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J312">
-        <v>479</v>
+        <v>310</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787741</t>
+          <t xml:space="preserve">311787745</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 7</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23451,30 +23451,30 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J313">
-        <v>310</v>
+        <v>470</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787745</t>
+          <t xml:space="preserve">311793891</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Margrethevej 5</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -23526,30 +23526,30 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">2171290</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J314">
-        <v>470</v>
+        <v>379</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793891</t>
+          <t xml:space="preserve">311827298</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-28</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 5</t>
+          <t xml:space="preserve">Kamstrupvej 1A</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171290</t>
+          <t xml:space="preserve">2170150</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -23610,21 +23610,21 @@
         </is>
       </c>
       <c r="J315">
-        <v>379</v>
+        <v>1122</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827298</t>
+          <t xml:space="preserve">311827519</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupvej 1A</t>
+          <t xml:space="preserve">Store Valbyvej 248B</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170150</t>
+          <t xml:space="preserve">2179764</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -23685,21 +23685,21 @@
         </is>
       </c>
       <c r="J316">
-        <v>1122</v>
+        <v>6510</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827519</t>
+          <t xml:space="preserve">311836213</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 248B</t>
+          <t xml:space="preserve">Baunehøjvej 9</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -23751,20 +23751,20 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179764</t>
+          <t xml:space="preserve">2174627</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J317">
-        <v>6510</v>
+        <v>410</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836213</t>
+          <t xml:space="preserve">311842230</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-07-02</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 9</t>
+          <t xml:space="preserve">Poppelgårdsvej 8</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -23826,30 +23826,30 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174627</t>
+          <t xml:space="preserve">100072983</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J318">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842230</t>
+          <t xml:space="preserve">311846096</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-02</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelgårdsvej 8</t>
+          <t xml:space="preserve">Bredgade 17B</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">100072983</t>
+          <t xml:space="preserve">5303694</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23910,11 +23910,11 @@
         </is>
       </c>
       <c r="J319">
-        <v>280</v>
+        <v>982</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846096</t>
+          <t xml:space="preserve">311848390</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-24</t>
+          <t xml:space="preserve">2035-08-11</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 17B</t>
+          <t xml:space="preserve">Ringstedgade 16</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303694</t>
+          <t xml:space="preserve">5303892</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -23985,11 +23985,11 @@
         </is>
       </c>
       <c r="J320">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848390</t>
+          <t xml:space="preserve">311848394</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 16</t>
+          <t xml:space="preserve">Ringstedgade 22</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303892</t>
+          <t xml:space="preserve">10239664</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -24060,11 +24060,11 @@
         </is>
       </c>
       <c r="J321">
-        <v>938</v>
+        <v>300</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848394</t>
+          <t xml:space="preserve">311848392</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 22</t>
+          <t xml:space="preserve">Margrethevej 7</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">10239664</t>
+          <t xml:space="preserve">2171297</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -24135,21 +24135,21 @@
         </is>
       </c>
       <c r="J322">
-        <v>300</v>
+        <v>8868</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848392</t>
+          <t xml:space="preserve">311848839</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-11</t>
+          <t xml:space="preserve">2035-08-13</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 7</t>
+          <t xml:space="preserve">Østre Kirkevej 7</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171297</t>
+          <t xml:space="preserve">2173901</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -24210,21 +24210,21 @@
         </is>
       </c>
       <c r="J323">
-        <v>8868</v>
+        <v>858</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848839</t>
+          <t xml:space="preserve">311871119</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-13</t>
+          <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24266,40 +24266,40 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kirkevej 7</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173901</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J324">
-        <v>858</v>
+        <v>1249</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871119</t>
+          <t xml:space="preserve">311878552</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-27</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24341,40 +24341,40 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Lises Markvej 2</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">100513466</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J325">
-        <v>1249</v>
+        <v>1387</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878552</t>
+          <t xml:space="preserve">311890892</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-03-27</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -24416,17 +24416,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lises Markvej 2</t>
+          <t xml:space="preserve">Hyldevænget 2</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513466</t>
+          <t xml:space="preserve">2213558</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -24435,21 +24435,21 @@
         </is>
       </c>
       <c r="J326">
-        <v>1387</v>
+        <v>530</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890892</t>
+          <t xml:space="preserve">311922906</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-27</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,17 +24491,17 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldevænget 2</t>
+          <t xml:space="preserve">Maglehøjen 6</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213558</t>
+          <t xml:space="preserve">5307587</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -24510,11 +24510,11 @@
         </is>
       </c>
       <c r="J327">
-        <v>530</v>
+        <v>1934</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922906</t>
+          <t xml:space="preserve">311925372</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglehøjen 6</t>
+          <t xml:space="preserve">Engbækvej 20</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -24576,30 +24576,30 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307587</t>
+          <t xml:space="preserve">9808161</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J328">
-        <v>1934</v>
+        <v>821</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925372</t>
+          <t xml:space="preserve">311928726</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">

--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agerskellet 13</t>
+          <t xml:space="preserve">Frederiksborgvej 561</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568845</t>
+          <t xml:space="preserve">2178448</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J141">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023910</t>
+          <t xml:space="preserve">200023938</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,40 +10616,40 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 561</t>
+          <t xml:space="preserve">Grantoften 3</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178448</t>
+          <t xml:space="preserve">2217322</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023938</t>
+          <t xml:space="preserve">200024857</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 3</t>
+          <t xml:space="preserve">Grantoften 5</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J143">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 5</t>
+          <t xml:space="preserve">Hyrdehøj 62</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217322</t>
+          <t xml:space="preserve">9113193</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>392</v>
+        <v>722</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024857</t>
+          <t xml:space="preserve">200024858</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 62</t>
+          <t xml:space="preserve">Kornvej 1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113193</t>
+          <t xml:space="preserve">8550293</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>722</v>
+        <v>812</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024858</t>
+          <t xml:space="preserve">200024855</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kornvej 1</t>
+          <t xml:space="preserve">Dommervænget 30</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550293</t>
+          <t xml:space="preserve">5306255</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>812</v>
+        <v>1225</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024855</t>
+          <t xml:space="preserve">200024872</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2019-12-02</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dommervænget 30</t>
+          <t xml:space="preserve">Bygaden 28</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306255</t>
+          <t xml:space="preserve">2178710</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>1225</v>
+        <v>263</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024872</t>
+          <t xml:space="preserve">200024953</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-02</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28</t>
+          <t xml:space="preserve">Gammel Darupvej 3</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178710</t>
+          <t xml:space="preserve">5307880</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>263</v>
+        <v>1383</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024953</t>
+          <t xml:space="preserve">200024956</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Darupvej 3</t>
+          <t xml:space="preserve">Lysalleen 33</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307880</t>
+          <t xml:space="preserve">8717244</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>1383</v>
+        <v>1298</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024956</t>
+          <t xml:space="preserve">200024948</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysalleen 33</t>
+          <t xml:space="preserve">Eriksvej 40C</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,20 +11226,20 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">8717244</t>
+          <t xml:space="preserve">5308364</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J150">
-        <v>1298</v>
+        <v>852</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024948</t>
+          <t xml:space="preserve">200024993</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 40C</t>
+          <t xml:space="preserve">Københavnsvej 106C</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,20 +11301,20 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308364</t>
+          <t xml:space="preserve">7896055</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>852</v>
+        <v>680</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024993</t>
+          <t xml:space="preserve">200024994</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 106C</t>
+          <t xml:space="preserve">Kamstrupsti 2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,30 +11376,30 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896055</t>
+          <t xml:space="preserve">5308151</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>680</v>
+        <v>400</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024994</t>
+          <t xml:space="preserve">200027969</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupsti 2</t>
+          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308151</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J153">
-        <v>400</v>
+        <v>995</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027969</t>
+          <t xml:space="preserve">200030999</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+          <t xml:space="preserve">BALSLEV</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2020-05-03</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
+          <t xml:space="preserve">Astersvej 9</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,30 +11526,30 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">5308975</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>995</v>
+        <v>4292</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030999</t>
+          <t xml:space="preserve">200049549</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALSLEV</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-03</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 9</t>
+          <t xml:space="preserve">Stændertorvet 1D</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,7 +11601,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308975</t>
+          <t xml:space="preserve">5304086</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,11 +11610,11 @@
         </is>
       </c>
       <c r="J155">
-        <v>4292</v>
+        <v>1906</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049549</t>
+          <t xml:space="preserve">200050785</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2021-06-29</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 1D</t>
+          <t xml:space="preserve">Mosestykket 21</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,20 +11676,20 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304086</t>
+          <t xml:space="preserve">2208892</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J156">
-        <v>1906</v>
+        <v>770</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050785</t>
+          <t xml:space="preserve">200051688</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-29</t>
+          <t xml:space="preserve">2021-08-03</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosestykket 21</t>
+          <t xml:space="preserve">Københavnsvej 266</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,30 +11751,30 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208892</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>770</v>
+        <v>573</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200051688</t>
+          <t xml:space="preserve">200057196</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve">Forum r.i.</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-03</t>
+          <t xml:space="preserve">2022-02-06</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266</t>
+          <t xml:space="preserve">Møllehusvej 13</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">8135053</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,21 +11835,21 @@
         </is>
       </c>
       <c r="J158">
-        <v>573</v>
+        <v>9546</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057196</t>
+          <t xml:space="preserve">200057529</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forum r.i.</t>
+          <t xml:space="preserve">TopDahl ApS</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-06</t>
+          <t xml:space="preserve">2022-02-20</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 13</t>
+          <t xml:space="preserve">Herregårdsvej 42</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8135053</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>9546</v>
+        <v>1898</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057529</t>
+          <t xml:space="preserve">200057621</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-20</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,17 +11966,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 42</t>
+          <t xml:space="preserve">Tranevej 7</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">7938930</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,21 +11985,21 @@
         </is>
       </c>
       <c r="J160">
-        <v>1898</v>
+        <v>638</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057621</t>
+          <t xml:space="preserve">200060567</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">TopDahl ApS</t>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 7</t>
+          <t xml:space="preserve">Baunegårdsvej 80</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,30 +12051,30 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938930</t>
+          <t xml:space="preserve">2179645</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J161">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060567</t>
+          <t xml:space="preserve">311052501</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-29</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,40 +12116,40 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 80</t>
+          <t xml:space="preserve">Højbakken 2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179645</t>
+          <t xml:space="preserve">10229610</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J162">
-        <v>677</v>
+        <v>620</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311052501</t>
+          <t xml:space="preserve">311060924</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12206,11 +12206,11 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J163">
-        <v>620</v>
+        <v>1226</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbakken 2</t>
+          <t xml:space="preserve">Baunehøjvej 5</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,30 +12276,30 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">10229610</t>
+          <t xml:space="preserve">2174626</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>1226</v>
+        <v>287</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311060924</t>
+          <t xml:space="preserve">311082107</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-23</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 5</t>
+          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174626</t>
+          <t xml:space="preserve">5309424</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>287</v>
+        <v>2196</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082107</t>
+          <t xml:space="preserve">311082106</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
+          <t xml:space="preserve">Himmelev Bygade 22C</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309424</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J166">
-        <v>2196</v>
+        <v>426</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082106</t>
+          <t xml:space="preserve">311082104</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 22C</t>
+          <t xml:space="preserve">Bistruphøj 2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,20 +12501,20 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">5312115</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J167">
-        <v>426</v>
+        <v>1048</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082104</t>
+          <t xml:space="preserve">311083539</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistruphøj 2</t>
+          <t xml:space="preserve">Bistrupvænge 16</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,25 +12576,25 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312115</t>
+          <t xml:space="preserve">5312015</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="J168">
-        <v>1048</v>
+        <v>927</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083539</t>
+          <t xml:space="preserve">311083529</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvænge 16</t>
+          <t xml:space="preserve">Lindegårdsparken 1</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">139</t>
         </is>
       </c>
       <c r="J169">
-        <v>927</v>
+        <v>20718</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsparken 1</t>
+          <t xml:space="preserve">Nygade 13</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,30 +12726,30 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312015</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>20718</v>
+        <v>568</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083529</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-14</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 13</t>
+          <t xml:space="preserve">Nygade 14</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J171">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 14</t>
+          <t xml:space="preserve">Nygade 18</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J172">
@@ -12941,30 +12941,30 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 18</t>
+          <t xml:space="preserve">Rosenhaven 13</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J173">
-        <v>568</v>
+        <v>268</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311098182</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 13</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2174669</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J174">
-        <v>268</v>
+        <v>401</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098182</t>
+          <t xml:space="preserve">311101306</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-03-17</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Sankt Ols Stræde 5</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174669</t>
+          <t xml:space="preserve">5303417</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,11 +13110,11 @@
         </is>
       </c>
       <c r="J175">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101306</t>
+          <t xml:space="preserve">311109494</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-17</t>
+          <t xml:space="preserve">2025-04-28</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 5</t>
+          <t xml:space="preserve">Strandgade 2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,20 +13176,20 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303417</t>
+          <t xml:space="preserve">5312664, 100884612</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J176">
-        <v>482</v>
+        <v>345</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109494</t>
+          <t xml:space="preserve">311110647</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-28</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 2</t>
+          <t xml:space="preserve">Lammegade 26</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312664, 100884612</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J177">
-        <v>345</v>
+        <v>667</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110647</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 26</t>
+          <t xml:space="preserve">Lammegade 28</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J178">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 28</t>
+          <t xml:space="preserve">Lammegade 30</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,11 +13406,11 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>667</v>
+        <v>496</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 30</t>
+          <t xml:space="preserve">Lammegade 36</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J180">
-        <v>496</v>
+        <v>624</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 36</t>
+          <t xml:space="preserve">Vestergade 6A</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">5312565</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>624</v>
+        <v>3282</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311115034</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 6A</t>
+          <t xml:space="preserve">Lyngbakken 1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312565</t>
+          <t xml:space="preserve">7175316</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>3282</v>
+        <v>362</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115034</t>
+          <t xml:space="preserve">311118205</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakken 1</t>
+          <t xml:space="preserve">Navervej 16</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">7175316</t>
+          <t xml:space="preserve">2209531</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -13710,11 +13710,11 @@
         </is>
       </c>
       <c r="J183">
-        <v>362</v>
+        <v>1432</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118205</t>
+          <t xml:space="preserve">311124782</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-10</t>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13781,11 +13781,11 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J184">
-        <v>1432</v>
+        <v>979</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navervej 16</t>
+          <t xml:space="preserve">Rabalderstræde 16</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209531</t>
+          <t xml:space="preserve">719145, 100067704</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,21 +13860,21 @@
         </is>
       </c>
       <c r="J185">
-        <v>979</v>
+        <v>3529</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124782</t>
+          <t xml:space="preserve">311137096</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-13</t>
+          <t xml:space="preserve">2025-09-28</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 16</t>
+          <t xml:space="preserve">Jernbanegade 21A</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,30 +13926,30 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">719145, 100067704</t>
+          <t xml:space="preserve">8995769</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>3529</v>
+        <v>1236</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311137096</t>
+          <t xml:space="preserve">311162791</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Klysner Consult ApS</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-28</t>
+          <t xml:space="preserve">2026-03-07</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 21A</t>
+          <t xml:space="preserve">Vestre Hedevej 32</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,40 +14001,40 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995769</t>
+          <t xml:space="preserve">719290, 100013803</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J187">
-        <v>1236</v>
+        <v>276</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311162791</t>
+          <t xml:space="preserve">311241595</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-07</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Hedevej 32</t>
+          <t xml:space="preserve">Basgangen 20</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,20 +14076,20 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">719290, 100013803</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="J188">
-        <v>276</v>
+        <v>2980</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241595</t>
+          <t xml:space="preserve">311351867</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2028-12-17</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basgangen 20</t>
+          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,30 +14151,30 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">100122346</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J189">
-        <v>2980</v>
+        <v>9549</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351867</t>
+          <t xml:space="preserve">311522399</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-17</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,40 +14216,40 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
+          <t xml:space="preserve">Søndergade 11</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">100122346</t>
+          <t xml:space="preserve">7855029</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J190">
-        <v>9549</v>
+        <v>1530</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522399</t>
+          <t xml:space="preserve">311552201</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,40 +14291,40 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 11</t>
+          <t xml:space="preserve">Sandhøjsvej 4</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7855029</t>
+          <t xml:space="preserve">1304635</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>1530</v>
+        <v>599</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552201</t>
+          <t xml:space="preserve">311569226</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandhøjsvej 4</t>
+          <t xml:space="preserve">Ramsømaglevej 17B</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304635</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>599</v>
+        <v>1459</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569226</t>
+          <t xml:space="preserve">311570325</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17B</t>
+          <t xml:space="preserve">Ramsømaglevej 17D</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14456,15 +14456,15 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J193">
-        <v>1459</v>
+        <v>355</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570325</t>
+          <t xml:space="preserve">311570327</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14516,40 +14516,40 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17D</t>
+          <t xml:space="preserve">Ejboparken 6</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J194">
-        <v>355</v>
+        <v>435</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570327</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6</t>
+          <t xml:space="preserve">Ejboparken 6B</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14606,11 +14606,11 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J195">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14681,11 +14681,11 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J196">
-        <v>517</v>
+        <v>258</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6B</t>
+          <t xml:space="preserve">Ejboparken 8A</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J197">
-        <v>258</v>
+        <v>477</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 8A</t>
+          <t xml:space="preserve">Hørhusene 61</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,20 +14826,20 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">5312139</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>477</v>
+        <v>826</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311595512</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørhusene 61</t>
+          <t xml:space="preserve">Københavnsvej 266C</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,30 +14901,30 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312139</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J199">
-        <v>826</v>
+        <v>322</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595512</t>
+          <t xml:space="preserve">311587049</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-22</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,40 +14966,40 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266C</t>
+          <t xml:space="preserve">Bueager 8</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">2211135</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J200">
-        <v>322</v>
+        <v>469</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587049</t>
+          <t xml:space="preserve">311608657</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">2032-06-17</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 8</t>
+          <t xml:space="preserve">Bueager 2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15056,15 +15056,15 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J201">
-        <v>469</v>
+        <v>4564</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311610029</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-17</t>
+          <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15131,11 +15131,11 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J202">
-        <v>4564</v>
+        <v>2127</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15206,11 +15206,11 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J203">
-        <v>2127</v>
+        <v>847</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 2</t>
+          <t xml:space="preserve">Bueager 6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15281,15 +15281,15 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J204">
-        <v>847</v>
+        <v>1898</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610029</t>
+          <t xml:space="preserve">311610041</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,40 +15341,40 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 6</t>
+          <t xml:space="preserve">Køgevej 106</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211135</t>
+          <t xml:space="preserve">5308417</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J205">
-        <v>1898</v>
+        <v>1620</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610041</t>
+          <t xml:space="preserve">311626283</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-23</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,40 +15416,40 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køgevej 106</t>
+          <t xml:space="preserve">Snoldelev Bygade 21B</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308417</t>
+          <t xml:space="preserve">2202050</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>1620</v>
+        <v>438</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626283</t>
+          <t xml:space="preserve">311633105</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snoldelev Bygade 21B</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202050</t>
+          <t xml:space="preserve">2170541</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>438</v>
+        <v>1257</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633105</t>
+          <t xml:space="preserve">311633102</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 65</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170541</t>
+          <t xml:space="preserve">8016122</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,21 +15585,21 @@
         </is>
       </c>
       <c r="J208">
-        <v>1257</v>
+        <v>2104</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633102</t>
+          <t xml:space="preserve">311645050</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-04</t>
+          <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15656,11 +15656,11 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J209">
-        <v>2104</v>
+        <v>434</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
+          <t xml:space="preserve">Gundsølillevej 2</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,30 +15726,30 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">8016122</t>
+          <t xml:space="preserve">2167605</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>434</v>
+        <v>979</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645050</t>
+          <t xml:space="preserve">311643576</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-08</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 2</t>
+          <t xml:space="preserve">Gundsølillevej 6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15806,15 +15806,15 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J211">
-        <v>979</v>
+        <v>4101</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643576</t>
+          <t xml:space="preserve">311643577</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 6</t>
+          <t xml:space="preserve">Sognevej 50</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,20 +15876,20 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167605</t>
+          <t xml:space="preserve">2172270</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>4101</v>
+        <v>3519</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643577</t>
+          <t xml:space="preserve">311644570</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,17 +15941,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 50</t>
+          <t xml:space="preserve">Planetvej 30</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172270</t>
+          <t xml:space="preserve">8907547</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,21 +15960,21 @@
         </is>
       </c>
       <c r="J213">
-        <v>3519</v>
+        <v>897</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644570</t>
+          <t xml:space="preserve">311644810</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">BOTJEK A/S</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-23</t>
+          <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16031,11 +16031,11 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J214">
-        <v>897</v>
+        <v>398</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -16106,11 +16106,11 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J215">
-        <v>398</v>
+        <v>1311</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J216">
-        <v>1311</v>
+        <v>924</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J217">
-        <v>924</v>
+        <v>487</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J218">
-        <v>487</v>
+        <v>256</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J219">
@@ -16481,11 +16481,11 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J220">
-        <v>256</v>
+        <v>897</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J221">
-        <v>897</v>
+        <v>983</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J222">
-        <v>983</v>
+        <v>552</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J223">
-        <v>552</v>
+        <v>897</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J224">
@@ -16856,11 +16856,11 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J225">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16931,11 +16931,11 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J226">
-        <v>898</v>
+        <v>280</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -17006,11 +17006,11 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J227">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -17081,11 +17081,11 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J228">
-        <v>900</v>
+        <v>789</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -17141,40 +17141,40 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planetvej 30</t>
+          <t xml:space="preserve">H H Kochs Vej 4</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">8907547</t>
+          <t xml:space="preserve">2173007</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J229">
-        <v>789</v>
+        <v>7796</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644810</t>
+          <t xml:space="preserve">311645058</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOTJEK A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-24</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">H H Kochs Vej 4</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173007</t>
+          <t xml:space="preserve">2180519</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17235,16 +17235,16 @@
         </is>
       </c>
       <c r="J230">
-        <v>7796</v>
+        <v>1448</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645058</t>
+          <t xml:space="preserve">311644999</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -17306,11 +17306,11 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J231">
-        <v>1448</v>
+        <v>413</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Lindelunden 1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180519</t>
+          <t xml:space="preserve">5306821</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,21 +17385,21 @@
         </is>
       </c>
       <c r="J232">
-        <v>413</v>
+        <v>5829</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644999</t>
+          <t xml:space="preserve">311645727</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindelunden 1</t>
+          <t xml:space="preserve">Trekroner Centervej 41</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17456,11 +17456,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>5829</v>
+        <v>12072</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17516,17 +17516,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Centervej 41</t>
+          <t xml:space="preserve">Ramsømaglevej 19</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306821</t>
+          <t xml:space="preserve">2213437</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,11 +17535,11 @@
         </is>
       </c>
       <c r="J234">
-        <v>12072</v>
+        <v>2744</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645727</t>
+          <t xml:space="preserve">311646168</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17606,15 +17606,15 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J235">
-        <v>2744</v>
+        <v>1287</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646168</t>
+          <t xml:space="preserve">311646167</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17666,30 +17666,30 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 19</t>
+          <t xml:space="preserve">Gammel Vindingevej 10</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213437</t>
+          <t xml:space="preserve">2209330</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J236">
-        <v>1287</v>
+        <v>5956</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646167</t>
+          <t xml:space="preserve">311646682</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17756,15 +17756,15 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J237">
-        <v>5956</v>
+        <v>447</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646682</t>
+          <t xml:space="preserve">311646683</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Vindingevej 10</t>
+          <t xml:space="preserve">Margrethekær 2</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17826,20 +17826,20 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209330</t>
+          <t xml:space="preserve">9700889</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J238">
-        <v>447</v>
+        <v>2442</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646683</t>
+          <t xml:space="preserve">311647649</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 2</t>
+          <t xml:space="preserve">Margrethekær 10</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17906,15 +17906,15 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J239">
-        <v>2442</v>
+        <v>1500</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647649</t>
+          <t xml:space="preserve">311647742</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 10</t>
+          <t xml:space="preserve">Margrethekær 12</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17981,11 +17981,11 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J240">
-        <v>1500</v>
+        <v>1517</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 12</t>
+          <t xml:space="preserve">Margrethekær 4</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J241">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 4</t>
+          <t xml:space="preserve">Margrethekær 6</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18131,11 +18131,11 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J242">
-        <v>1514</v>
+        <v>1500</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 6</t>
+          <t xml:space="preserve">Margrethekær 8</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18206,11 +18206,11 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J243">
-        <v>1500</v>
+        <v>1577</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 8</t>
+          <t xml:space="preserve">Hyrdehøj 3</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,30 +18276,30 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700889</t>
+          <t xml:space="preserve">7713101</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>1577</v>
+        <v>11744</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647742</t>
+          <t xml:space="preserve">311649946</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18356,15 +18356,15 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J245">
-        <v>11744</v>
+        <v>1185</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649946</t>
+          <t xml:space="preserve">311649970</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2032-12-18</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 3</t>
+          <t xml:space="preserve">Møllehusvej 118</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,30 +18426,30 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">7713101</t>
+          <t xml:space="preserve">258624, 258625</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J246">
-        <v>1185</v>
+        <v>4232</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649970</t>
+          <t xml:space="preserve">311650857</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-18</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,17 +18491,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 118</t>
+          <t xml:space="preserve">Kirkebjergvej 2</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">258624, 258625</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,11 +18510,11 @@
         </is>
       </c>
       <c r="J247">
-        <v>4232</v>
+        <v>1786</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650857</t>
+          <t xml:space="preserve">311652564</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 2</t>
+          <t xml:space="preserve">Kirkebjergvej 4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18581,15 +18581,15 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J248">
-        <v>1786</v>
+        <v>1585</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652564</t>
+          <t xml:space="preserve">311652563</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 4</t>
+          <t xml:space="preserve">Kirkebjergvej 6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18656,15 +18656,15 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J249">
-        <v>1585</v>
+        <v>2239</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652563</t>
+          <t xml:space="preserve">311652567</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 6</t>
+          <t xml:space="preserve">Kirkebjergvej 8</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18731,15 +18731,15 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J250">
-        <v>2239</v>
+        <v>610</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652567</t>
+          <t xml:space="preserve">311652565</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,40 +18791,40 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 8</t>
+          <t xml:space="preserve">Ørstedvej 63B</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>610</v>
+        <v>8368</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652565</t>
+          <t xml:space="preserve">311652748</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-01-06</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,40 +18866,40 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63B</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J252">
-        <v>8368</v>
+        <v>1815</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652748</t>
+          <t xml:space="preserve">311652906</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-06</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18956,11 +18956,11 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J253">
-        <v>1815</v>
+        <v>2850</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -19031,11 +19031,11 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J254">
-        <v>2850</v>
+        <v>1908</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -19091,40 +19091,40 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">5304953</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J255">
-        <v>1908</v>
+        <v>6173</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652906</t>
+          <t xml:space="preserve">311656342</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 14</t>
+          <t xml:space="preserve">Københavnsvej 34</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304953</t>
+          <t xml:space="preserve">5311321</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,21 +19185,21 @@
         </is>
       </c>
       <c r="J256">
-        <v>6173</v>
+        <v>9899</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656342</t>
+          <t xml:space="preserve">311655694</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 34</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,25 +19251,25 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311321</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J257">
-        <v>9899</v>
+        <v>9084</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655694</t>
+          <t xml:space="preserve">311655558</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Bymarken 37</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19326,20 +19326,20 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5306248</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J258">
-        <v>9084</v>
+        <v>8569</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655558</t>
+          <t xml:space="preserve">311656548</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymarken 37</t>
+          <t xml:space="preserve">Gormsvej 9B</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,20 +19401,20 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306248</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J259">
-        <v>8569</v>
+        <v>440</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656548</t>
+          <t xml:space="preserve">311656782</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 9B</t>
+          <t xml:space="preserve">Rådhusbuen 3</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19481,15 +19481,15 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J260">
-        <v>440</v>
+        <v>5709</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656782</t>
+          <t xml:space="preserve">311657131</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-30</t>
+          <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 3</t>
+          <t xml:space="preserve">Munkebro 2</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,20 +19551,20 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5303415</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J261">
-        <v>5709</v>
+        <v>608</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657131</t>
+          <t xml:space="preserve">311657447</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-31</t>
+          <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkebro 2</t>
+          <t xml:space="preserve">Sankt Ols Stræde 3</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19631,15 +19631,15 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J262">
-        <v>608</v>
+        <v>858</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657447</t>
+          <t xml:space="preserve">311657449</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19706,15 +19706,15 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J263">
-        <v>858</v>
+        <v>433</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657449</t>
+          <t xml:space="preserve">311657448</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 3</t>
+          <t xml:space="preserve">Absalonsgade 1</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303415</t>
+          <t xml:space="preserve">8995768</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -19785,21 +19785,21 @@
         </is>
       </c>
       <c r="J264">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657448</t>
+          <t xml:space="preserve">311659172</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-01</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 1</t>
+          <t xml:space="preserve">Absalonsgade 2</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19856,11 +19856,11 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J265">
-        <v>378</v>
+        <v>6187</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 2</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995768</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,21 +19935,21 @@
         </is>
       </c>
       <c r="J266">
-        <v>6187</v>
+        <v>9651</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659172</t>
+          <t xml:space="preserve">311666198</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-14</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,17 +19991,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Baunegårdsvej 85</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,21 +20010,21 @@
         </is>
       </c>
       <c r="J267">
-        <v>9651</v>
+        <v>3340</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666198</t>
+          <t xml:space="preserve">311664732</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-14</t>
+          <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20081,11 +20081,11 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J268">
-        <v>3340</v>
+        <v>916</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -20156,11 +20156,11 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J269">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -20231,11 +20231,11 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J270">
-        <v>900</v>
+        <v>711</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -20306,11 +20306,11 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J271">
-        <v>711</v>
+        <v>1816</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 85</t>
+          <t xml:space="preserve">Lynghøjen 107A</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J272">
-        <v>1816</v>
+        <v>817</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664732</t>
+          <t xml:space="preserve">311665647</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-07</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107A</t>
+          <t xml:space="preserve">Lynghøjen 107B</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20456,15 +20456,15 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J273">
-        <v>817</v>
+        <v>1552</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665647</t>
+          <t xml:space="preserve">311665669</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107B</t>
+          <t xml:space="preserve">Lynghøjen 107C</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20531,11 +20531,11 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J274">
-        <v>1552</v>
+        <v>433</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107C</t>
+          <t xml:space="preserve">Lynghøjen 107</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20606,15 +20606,15 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J275">
-        <v>433</v>
+        <v>12308</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665669</t>
+          <t xml:space="preserve">311666274</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-03-14</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107</t>
+          <t xml:space="preserve">Industrileddet 4</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">2180546</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20685,21 +20685,21 @@
         </is>
       </c>
       <c r="J276">
-        <v>12308</v>
+        <v>2200</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666274</t>
+          <t xml:space="preserve">311666541</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-14</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrileddet 4</t>
+          <t xml:space="preserve">Ollerupvej 5</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180546</t>
+          <t xml:space="preserve">2173759</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -20760,21 +20760,21 @@
         </is>
       </c>
       <c r="J277">
-        <v>2200</v>
+        <v>12044</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666541</t>
+          <t xml:space="preserve">311667669</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-03-20</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20831,11 +20831,11 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J278">
-        <v>12044</v>
+        <v>494</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 5</t>
+          <t xml:space="preserve">Ollerupvej 7</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20906,15 +20906,15 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J279">
-        <v>494</v>
+        <v>826</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667669</t>
+          <t xml:space="preserve">311667621</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 7</t>
+          <t xml:space="preserve">Helligkorsvej 42A</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20976,20 +20976,20 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173759</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J280">
-        <v>826</v>
+        <v>3137</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667621</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20999,7 +20999,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-20</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21056,11 +21056,11 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J281">
-        <v>3137</v>
+        <v>6340</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -21131,11 +21131,11 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J282">
-        <v>6340</v>
+        <v>2165</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42A</t>
+          <t xml:space="preserve">Helligkorsvej 42C</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -21206,11 +21206,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J283">
-        <v>2165</v>
+        <v>778</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42C</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -21276,20 +21276,20 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>778</v>
+        <v>2177</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21356,11 +21356,11 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J285">
-        <v>2177</v>
+        <v>3318</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -21431,11 +21431,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J286">
-        <v>3318</v>
+        <v>766</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Østre Vindingevej 221C</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21506,15 +21506,15 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J287">
-        <v>766</v>
+        <v>2100</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670926</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221C</t>
+          <t xml:space="preserve">Bistrup Bakke 5</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -21576,30 +21576,30 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">100513814</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">109</t>
         </is>
       </c>
       <c r="J288">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670926</t>
+          <t xml:space="preserve">311673245</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 5</t>
+          <t xml:space="preserve">Bistrup Bakke 3</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21656,15 +21656,15 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">109</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="J289">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673245</t>
+          <t xml:space="preserve">311675948</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 3</t>
+          <t xml:space="preserve">Bistrup Bakke 7</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -21731,15 +21731,15 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J290">
-        <v>997</v>
+        <v>1077</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675948</t>
+          <t xml:space="preserve">311675950</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 7</t>
+          <t xml:space="preserve">Astersvej 15</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21801,30 +21801,30 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513814</t>
+          <t xml:space="preserve">8995869</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J291">
-        <v>1077</v>
+        <v>10347</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675950</t>
+          <t xml:space="preserve">311676003</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-24</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -21881,11 +21881,11 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J292">
-        <v>10347</v>
+        <v>6038</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15</t>
+          <t xml:space="preserve">Astersvej 15C</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21956,15 +21956,15 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J293">
-        <v>6038</v>
+        <v>643</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676003</t>
+          <t xml:space="preserve">311676217</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -22016,30 +22016,30 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 15C</t>
+          <t xml:space="preserve">Ørstedvej 63A</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995869</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J294">
-        <v>643</v>
+        <v>585</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676217</t>
+          <t xml:space="preserve">311679099</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -22091,30 +22091,30 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 63A</t>
+          <t xml:space="preserve">Kongebakken 19</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J295">
-        <v>585</v>
+        <v>6671</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679099</t>
+          <t xml:space="preserve">311683094</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-25</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19</t>
+          <t xml:space="preserve">Kongebakken 19A</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">9306001</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -22185,11 +22185,11 @@
         </is>
       </c>
       <c r="J296">
-        <v>6671</v>
+        <v>630</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683094</t>
+          <t xml:space="preserve">311683580</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-25</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongebakken 19A</t>
+          <t xml:space="preserve">Trekroner Alle 1</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306001</t>
+          <t xml:space="preserve">2174448</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -22260,11 +22260,11 @@
         </is>
       </c>
       <c r="J297">
-        <v>630</v>
+        <v>1216</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683580</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-26</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22331,11 +22331,11 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J298">
-        <v>1216</v>
+        <v>1537</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -22406,11 +22406,11 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J299">
-        <v>1537</v>
+        <v>962</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -22481,11 +22481,11 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J300">
-        <v>962</v>
+        <v>3144</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -22556,11 +22556,11 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J301">
-        <v>3144</v>
+        <v>929</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -22631,11 +22631,11 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J302">
-        <v>929</v>
+        <v>553</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -22706,11 +22706,11 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J303">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -22781,15 +22781,15 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J304">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725441</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22856,15 +22856,15 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J305">
-        <v>599</v>
+        <v>715</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725441</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1</t>
+          <t xml:space="preserve">Trekroner Alle 1C</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -22931,15 +22931,15 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J306">
-        <v>715</v>
+        <v>2011</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725438</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1C</t>
+          <t xml:space="preserve">Piledyssen 50</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23001,30 +23001,30 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174448</t>
+          <t xml:space="preserve">2172114</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J307">
-        <v>2011</v>
+        <v>595</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725438</t>
+          <t xml:space="preserve">311743780</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piledyssen 50</t>
+          <t xml:space="preserve">Vindeboder 7</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23076,30 +23076,30 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172114</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J308">
-        <v>595</v>
+        <v>686</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743780</t>
+          <t xml:space="preserve">311787742</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-07</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23156,11 +23156,11 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J309">
-        <v>686</v>
+        <v>452</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -23231,15 +23231,15 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J310">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787742</t>
+          <t xml:space="preserve">311787741</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23306,15 +23306,15 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J311">
-        <v>479</v>
+        <v>310</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787741</t>
+          <t xml:space="preserve">311787745</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 7</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -23376,30 +23376,30 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J312">
-        <v>310</v>
+        <v>470</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787745</t>
+          <t xml:space="preserve">311793891</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Margrethevej 5</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23451,30 +23451,30 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">2171290</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J313">
-        <v>470</v>
+        <v>379</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793891</t>
+          <t xml:space="preserve">311827298</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-28</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 5</t>
+          <t xml:space="preserve">Kamstrupvej 1A</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -23526,7 +23526,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171290</t>
+          <t xml:space="preserve">2170150</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -23535,21 +23535,21 @@
         </is>
       </c>
       <c r="J314">
-        <v>379</v>
+        <v>1122</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827298</t>
+          <t xml:space="preserve">311827519</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupvej 1A</t>
+          <t xml:space="preserve">Store Valbyvej 248B</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170150</t>
+          <t xml:space="preserve">2179764</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -23610,21 +23610,21 @@
         </is>
       </c>
       <c r="J315">
-        <v>1122</v>
+        <v>6510</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827519</t>
+          <t xml:space="preserve">311836213</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 248B</t>
+          <t xml:space="preserve">Baunehøjvej 9</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -23676,20 +23676,20 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179764</t>
+          <t xml:space="preserve">2174627</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J316">
-        <v>6510</v>
+        <v>410</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836213</t>
+          <t xml:space="preserve">311842230</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-07-02</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 9</t>
+          <t xml:space="preserve">Poppelgårdsvej 8</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -23751,30 +23751,30 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174627</t>
+          <t xml:space="preserve">100072983</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J317">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842230</t>
+          <t xml:space="preserve">311846096</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Norca Aps</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-02</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelgårdsvej 8</t>
+          <t xml:space="preserve">Bredgade 17B</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">100072983</t>
+          <t xml:space="preserve">5303694</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -23835,11 +23835,11 @@
         </is>
       </c>
       <c r="J318">
-        <v>280</v>
+        <v>982</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846096</t>
+          <t xml:space="preserve">311848390</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23849,7 +23849,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-24</t>
+          <t xml:space="preserve">2035-08-11</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 17B</t>
+          <t xml:space="preserve">Ringstedgade 16</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303694</t>
+          <t xml:space="preserve">5303892</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23910,11 +23910,11 @@
         </is>
       </c>
       <c r="J319">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848390</t>
+          <t xml:space="preserve">311848394</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 16</t>
+          <t xml:space="preserve">Ringstedgade 22</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303892</t>
+          <t xml:space="preserve">10239664</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -23985,11 +23985,11 @@
         </is>
       </c>
       <c r="J320">
-        <v>938</v>
+        <v>300</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848394</t>
+          <t xml:space="preserve">311848392</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 22</t>
+          <t xml:space="preserve">Margrethevej 7</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,7 +24051,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">10239664</t>
+          <t xml:space="preserve">2171297</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -24060,21 +24060,21 @@
         </is>
       </c>
       <c r="J321">
-        <v>300</v>
+        <v>8868</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848392</t>
+          <t xml:space="preserve">311848839</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca Aps</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-11</t>
+          <t xml:space="preserve">2035-08-13</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 7</t>
+          <t xml:space="preserve">Østre Kirkevej 7</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171297</t>
+          <t xml:space="preserve">2173901</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -24135,21 +24135,21 @@
         </is>
       </c>
       <c r="J322">
-        <v>8868</v>
+        <v>858</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848839</t>
+          <t xml:space="preserve">311871119</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-13</t>
+          <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24191,40 +24191,40 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kirkevej 7</t>
+          <t xml:space="preserve">Ramsømaglevej 17C</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173901</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J323">
-        <v>858</v>
+        <v>1249</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871119</t>
+          <t xml:space="preserve">311878552</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-27</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24266,40 +24266,40 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17C</t>
+          <t xml:space="preserve">Lises Markvej 2</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">100513466</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J324">
-        <v>1249</v>
+        <v>1387</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878552</t>
+          <t xml:space="preserve">311890892</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">e-consult ApS</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-03-27</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24341,17 +24341,17 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lises Markvej 2</t>
+          <t xml:space="preserve">Hyldevænget 2</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513466</t>
+          <t xml:space="preserve">2213558</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -24360,21 +24360,21 @@
         </is>
       </c>
       <c r="J325">
-        <v>1387</v>
+        <v>530</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311890892</t>
+          <t xml:space="preserve">311922906</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">e-consult ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-27</t>
+          <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -24416,17 +24416,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldevænget 2</t>
+          <t xml:space="preserve">Maglehøjen 6</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213558</t>
+          <t xml:space="preserve">5307587</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -24435,11 +24435,11 @@
         </is>
       </c>
       <c r="J326">
-        <v>530</v>
+        <v>1934</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922906</t>
+          <t xml:space="preserve">311925372</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -24449,7 +24449,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-01</t>
+          <t xml:space="preserve">2036-09-11</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,7 +24491,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglehøjen 6</t>
+          <t xml:space="preserve">Engbækvej 20</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -24501,30 +24501,30 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307587</t>
+          <t xml:space="preserve">9808161</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J327">
-        <v>1934</v>
+        <v>821</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925372</t>
+          <t xml:space="preserve">311928726</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-11</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -24566,30 +24566,30 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbækvej 20</t>
+          <t xml:space="preserve">Agerskellet 13</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808161</t>
+          <t xml:space="preserve">7568845</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J328">
-        <v>821</v>
+        <v>354</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928726</t>
+          <t xml:space="preserve">311931597</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-29</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
